--- a/Spider Menu Letter Map.xlsx
+++ b/Spider Menu Letter Map.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c595d08442566827/Documents/aaSpider Solving/SpiderConsole/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/C595D08442566827/Documents/aaSpider Solving/SpiderConsole/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="34" documentId="8_{42D75DCC-4025-455C-94D1-56D6E061E20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CFEBB33F-5D01-4339-A3AD-E21E31C0E04C}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{42D75DCC-4025-455C-94D1-56D6E061E20C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE1BE775-6066-43F0-BEE2-B129B2E5A417}"/>
   <bookViews>
-    <workbookView xWindow="13710" yWindow="600" windowWidth="6435" windowHeight="10920" xr2:uid="{2CF26FA7-EB63-4C7A-AADB-1E2F6DA3EEDF}"/>
+    <workbookView xWindow="2820" yWindow="885" windowWidth="8280" windowHeight="10515" xr2:uid="{2CF26FA7-EB63-4C7A-AADB-1E2F6DA3EEDF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="55">
   <si>
     <t>A</t>
   </si>
@@ -189,6 +189,21 @@
   </si>
   <si>
     <t>todo</t>
+  </si>
+  <si>
+    <t>StatsMenu</t>
+  </si>
+  <si>
+    <t>save stats</t>
+  </si>
+  <si>
+    <t>load stats</t>
+  </si>
+  <si>
+    <t>show stats</t>
+  </si>
+  <si>
+    <t>reset stats</t>
   </si>
 </sst>
 </file>
@@ -628,20 +643,44 @@
       <c r="A9" t="s">
         <v>5</v>
       </c>
+      <c r="C9" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>6</v>
       </c>
+      <c r="C10" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
+      <c r="C11" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
+      </c>
+      <c r="C12" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
